--- a/配置核查表_v2.0.0_标注自动验证.xlsx
+++ b/配置核查表_v2.0.0_标注自动验证.xlsx
@@ -1272,7 +1272,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="187" customHeight="1" s="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>本表填写说明及作业指导书要求：
 1、若某个检查项适用于右侧的检查对象，则在对应检查项行、对应检查项列打“勾”；缺乏资料尚未完成核查，对应项空白；经验证无需核查的项打“—”
